--- a/astro-site/public/dl/guia-panaderia-obrador/escandallo-maestro-panaderia.xlsx
+++ b/astro-site/public/dl/guia-panaderia-obrador/escandallo-maestro-panaderia.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escandallos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Escandallos'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -451,7 +453,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -473,6 +475,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -532,15 +535,15 @@
       </c>
       <c r="E4" s="3">
         <f>C4/D4</f>
-        <v/>
+        <v>0.1727272727272727</v>
       </c>
       <c r="F4" s="3">
         <f>1-E4</f>
-        <v/>
+        <v>0.8272727272727273</v>
       </c>
       <c r="G4">
         <f>D4-C4</f>
-        <v/>
+        <v>1.8200000000000003</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -565,15 +568,15 @@
       </c>
       <c r="E5" s="3">
         <f>C5/D5</f>
-        <v/>
+        <v>0.15714285714285717</v>
       </c>
       <c r="F5" s="3">
         <f>1-E5</f>
-        <v/>
+        <v>0.8428571428571429</v>
       </c>
       <c r="G5">
         <f>D5-C5</f>
-        <v/>
+        <v>2.95</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -598,15 +601,15 @@
       </c>
       <c r="E6" s="3">
         <f>C6/D6</f>
-        <v/>
+        <v>0.1854838709677419</v>
       </c>
       <c r="F6" s="3">
         <f>1-E6</f>
-        <v/>
+        <v>0.8145161290322581</v>
       </c>
       <c r="G6">
         <f>D6-C6</f>
-        <v/>
+        <v>5.050000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -631,15 +634,15 @@
       </c>
       <c r="E7" s="3">
         <f>C7/D7</f>
-        <v/>
+        <v>0.1794871794871795</v>
       </c>
       <c r="F7" s="3">
         <f>1-E7</f>
-        <v/>
+        <v>0.8205128205128205</v>
       </c>
       <c r="G7">
         <f>D7-C7</f>
-        <v/>
+        <v>6.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -664,15 +667,15 @@
       </c>
       <c r="E8" s="3">
         <f>C8/D8</f>
-        <v/>
+        <v>0.22222222222222224</v>
       </c>
       <c r="F8" s="3">
         <f>1-E8</f>
-        <v/>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G8">
         <f>D8-C8</f>
-        <v/>
+        <v>5.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -697,15 +700,15 @@
       </c>
       <c r="E9" s="3">
         <f>C9/D9</f>
-        <v/>
+        <v>0.19594594594594594</v>
       </c>
       <c r="F9" s="3">
         <f>1-E9</f>
-        <v/>
+        <v>0.8040540540540541</v>
       </c>
       <c r="G9">
         <f>D9-C9</f>
-        <v/>
+        <v>5.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -730,15 +733,15 @@
       </c>
       <c r="E10" s="3">
         <f>C10/D10</f>
-        <v/>
+        <v>0.14473684210526316</v>
       </c>
       <c r="F10" s="3">
         <f>1-E10</f>
-        <v/>
+        <v>0.8552631578947368</v>
       </c>
       <c r="G10">
         <f>D10-C10</f>
-        <v/>
+        <v>3.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -763,15 +766,15 @@
       </c>
       <c r="E11" s="3">
         <f>C11/D11</f>
-        <v/>
+        <v>0.08636363636363636</v>
       </c>
       <c r="F11" s="3">
         <f>1-E11</f>
-        <v/>
+        <v>0.9136363636363636</v>
       </c>
       <c r="G11">
         <f>D11-C11</f>
-        <v/>
+        <v>20.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -796,15 +799,15 @@
       </c>
       <c r="E12" s="3">
         <f>C12/D12</f>
-        <v/>
+        <v>0.20370370370370372</v>
       </c>
       <c r="F12" s="3">
         <f>1-E12</f>
-        <v/>
+        <v>0.7962962962962963</v>
       </c>
       <c r="G12">
         <f>D12-C12</f>
-        <v/>
+        <v>4.300000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -829,15 +832,15 @@
       </c>
       <c r="E13" s="3">
         <f>C13/D13</f>
-        <v/>
+        <v>0.2571428571428572</v>
       </c>
       <c r="F13" s="3">
         <f>1-E13</f>
-        <v/>
+        <v>0.7428571428571429</v>
       </c>
       <c r="G13">
         <f>D13-C13</f>
-        <v/>
+        <v>5.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -862,15 +865,15 @@
       </c>
       <c r="E14" s="3">
         <f>C14/D14</f>
-        <v/>
+        <v>0.21551724137931036</v>
       </c>
       <c r="F14" s="3">
         <f>1-E14</f>
-        <v/>
+        <v>0.7844827586206896</v>
       </c>
       <c r="G14">
         <f>D14-C14</f>
-        <v/>
+        <v>4.55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -895,15 +898,15 @@
       </c>
       <c r="E15" s="3">
         <f>C15/D15</f>
-        <v/>
+        <v>0.20454545454545453</v>
       </c>
       <c r="F15" s="3">
         <f>1-E15</f>
-        <v/>
+        <v>0.7954545454545454</v>
       </c>
       <c r="G15">
         <f>D15-C15</f>
-        <v/>
+        <v>1.7500000000000002</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -928,15 +931,15 @@
       </c>
       <c r="E16" s="3">
         <f>C16/D16</f>
-        <v/>
+        <v>0.22916666666666669</v>
       </c>
       <c r="F16" s="3">
         <f>1-E16</f>
-        <v/>
+        <v>0.7708333333333333</v>
       </c>
       <c r="G16">
         <f>D16-C16</f>
-        <v/>
+        <v>1.8499999999999999</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -961,15 +964,15 @@
       </c>
       <c r="E17" s="3">
         <f>C17/D17</f>
-        <v/>
+        <v>0.21874999999999997</v>
       </c>
       <c r="F17" s="3">
         <f>1-E17</f>
-        <v/>
+        <v>0.78125</v>
       </c>
       <c r="G17">
         <f>D17-C17</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -994,15 +997,15 @@
       </c>
       <c r="E18" s="3">
         <f>C18/D18</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="F18" s="3">
         <f>1-E18</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="G18">
         <f>D18-C18</f>
-        <v/>
+        <v>1.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1027,15 +1030,15 @@
       </c>
       <c r="E19" s="3">
         <f>C19/D19</f>
-        <v/>
+        <v>0.18666666666666668</v>
       </c>
       <c r="F19" s="3">
         <f>1-E19</f>
-        <v/>
+        <v>0.8133333333333334</v>
       </c>
       <c r="G19">
         <f>D19-C19</f>
-        <v/>
+        <v>1.22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1060,15 +1063,15 @@
       </c>
       <c r="E20" s="3">
         <f>C20/D20</f>
-        <v/>
+        <v>0.22727272727272727</v>
       </c>
       <c r="F20" s="3">
         <f>1-E20</f>
-        <v/>
+        <v>0.7727272727272727</v>
       </c>
       <c r="G20">
         <f>D20-C20</f>
-        <v/>
+        <v>1.7000000000000002</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1093,15 +1096,15 @@
       </c>
       <c r="E21" s="3">
         <f>C21/D21</f>
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="F21" s="3">
         <f>1-E21</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="G21">
         <f>D21-C21</f>
-        <v/>
+        <v>1.9500000000000002</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1126,15 +1129,15 @@
       </c>
       <c r="E22" s="3">
         <f>C22/D22</f>
-        <v/>
+        <v>0.3088235294117647</v>
       </c>
       <c r="F22" s="3">
         <f>1-E22</f>
-        <v/>
+        <v>0.6911764705882353</v>
       </c>
       <c r="G22">
         <f>D22-C22</f>
-        <v/>
+        <v>2.3499999999999996</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1159,15 +1162,15 @@
       </c>
       <c r="E23" s="3">
         <f>C23/D23</f>
-        <v/>
+        <v>0.2638888888888889</v>
       </c>
       <c r="F23" s="3">
         <f>1-E23</f>
-        <v/>
+        <v>0.7361111111111112</v>
       </c>
       <c r="G23">
         <f>D23-C23</f>
-        <v/>
+        <v>2.6500000000000004</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1192,15 +1195,15 @@
       </c>
       <c r="E24" s="3">
         <f>C24/D24</f>
-        <v/>
+        <v>0.2236842105263158</v>
       </c>
       <c r="F24" s="3">
         <f>1-E24</f>
-        <v/>
+        <v>0.7763157894736842</v>
       </c>
       <c r="G24">
         <f>D24-C24</f>
-        <v/>
+        <v>2.9499999999999997</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1225,17 +1228,16 @@
       </c>
       <c r="E25" s="3">
         <f>C25/D25</f>
-        <v/>
+        <v>0.09999999999999999</v>
       </c>
       <c r="F25" s="3">
         <f>1-E25</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="G25">
         <f>D25-C25</f>
-        <v/>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>1.62</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1254,15 +1256,15 @@
       </c>
       <c r="E26" s="3">
         <f>C26/D26</f>
-        <v/>
+        <v>0.13749999999999998</v>
       </c>
       <c r="F26" s="3">
         <f>1-E26</f>
-        <v/>
+        <v>0.8625</v>
       </c>
       <c r="G26">
         <f>D26-C26</f>
-        <v/>
+        <v>1.3800000000000001</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1287,15 +1289,15 @@
       </c>
       <c r="E27" s="3">
         <f>C27/D27</f>
-        <v/>
+        <v>0.13124999999999998</v>
       </c>
       <c r="F27" s="3">
         <f>1-E27</f>
-        <v/>
+        <v>0.86875</v>
       </c>
       <c r="G27">
         <f>D27-C27</f>
-        <v/>
+        <v>2.7800000000000002</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1320,15 +1322,15 @@
       </c>
       <c r="E28" s="3">
         <f>C28/D28</f>
-        <v/>
+        <v>0.2421875</v>
       </c>
       <c r="F28" s="3">
         <f>1-E28</f>
-        <v/>
+        <v>0.7578125</v>
       </c>
       <c r="G28">
         <f>D28-C28</f>
-        <v/>
+        <v>4.8500000000000005</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1340,6 +1342,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>